--- a/InputData/trans/EVCRSbRIC/EV Charger Revenue Share by Recip ISIC Code.xlsx
+++ b/InputData/trans/EVCRSbRIC/EV Charger Revenue Share by Recip ISIC Code.xlsx
@@ -1,33 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\trans\EVCRSbRIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\isic52-staging\trans\EVCRSbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6493CFD-7C39-4D67-A92E-8BFC2549E335}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0DCE35897183B32C88B2F7DBDC84B1138DA8992B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="105" windowWidth="25665" windowHeight="16830" xr2:uid="{6DD38E28-D572-4B43-9762-4D2A32B496C8}"/>
+    <workbookView xWindow="0" yWindow="1830" windowWidth="43200" windowHeight="17025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="DOE Data and Calcs" sheetId="3" r:id="rId2"/>
-    <sheet name="EVCRSbRIC" sheetId="2" r:id="rId3"/>
+    <sheet name="Factors applied" sheetId="2" r:id="rId2"/>
+    <sheet name="DOE Data and Calcs" sheetId="3" r:id="rId3"/>
+    <sheet name="Checks" sheetId="4" r:id="rId4"/>
+    <sheet name="EVCRSbRIC" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>EVCRSbRIC EV Charger Revenue Share by Recipient ISIC Code</t>
   </si>
@@ -43,25 +45,226 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>Costs Associated With Non-Residential Electric Vehicle Supply Equipment</t>
+  </si>
+  <si>
+    <t>https://afdc.energy.gov/files/u/publication/evse_cost_report_2015.pdf</t>
+  </si>
+  <si>
     <t>Page 13</t>
   </si>
   <si>
-    <t>https://afdc.energy.gov/files/u/publication/evse_cost_report_2015.pdf</t>
-  </si>
-  <si>
-    <t>U.S. Department of Energy</t>
-  </si>
-  <si>
-    <t>Costs Associated With Non-Residential Electric Vehicle Supply Equipment</t>
+    <t>52-code expansion (2026-07-17):</t>
+  </si>
+  <si>
+    <t>The output tabs produce the 52-code ISIC list. The derivation above is unchanged and live; output-tab formulas reference the derivation tabs</t>
+  </si>
+  <si>
+    <t>directly, with the original header-label criteria written as literals (the derivation tabs still use the pre-split 42-code labels).</t>
+  </si>
+  <si>
+    <t>Children of split parents multiply the parent's allocation by the factors on the 'Factors applied' tab (editable; defaults = BEA 2024 gross-</t>
+  </si>
+  <si>
+    <t>output shares from io-model/BObIC; semantic overrides documented per row with rationale).</t>
+  </si>
+  <si>
+    <t>Child factors applied inline in the output-tab formulas (editable). Defaults = BEA 2024 output shares; semantic overrides and fuel reroutes noted per row.</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Row context</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>BEA 2024 output share</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv</t>
+  </si>
+  <si>
+    <t>Share of Costs by ISIC Code</t>
+  </si>
+  <si>
+    <t>ISIC 01</t>
+  </si>
+  <si>
+    <t>ISIC 01T03</t>
+  </si>
+  <si>
+    <t>BEA 2024 output share (default)</t>
+  </si>
+  <si>
+    <t>ISIC 02</t>
+  </si>
+  <si>
+    <t>ISIC 03</t>
+  </si>
+  <si>
+    <t>ISIC 07</t>
+  </si>
+  <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
+    <t>ISIC 08</t>
+  </si>
+  <si>
+    <t>ISIC 301</t>
+  </si>
+  <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
+    <t>ISIC 302T309</t>
+  </si>
+  <si>
+    <t>ISIC 49</t>
+  </si>
+  <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
+    <t>ISIC 50</t>
+  </si>
+  <si>
+    <t>ISIC 51</t>
+  </si>
+  <si>
+    <t>ISIC 52</t>
+  </si>
+  <si>
+    <t>ISIC 53</t>
+  </si>
+  <si>
+    <t>ISIC 69T75</t>
+  </si>
+  <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
+    <t>semantic override</t>
+  </si>
+  <si>
+    <t>ISIC 77T82</t>
+  </si>
+  <si>
+    <t>ISIC 90T93</t>
+  </si>
+  <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
+    <t>ISIC 94T96</t>
+  </si>
+  <si>
+    <t>DOE Cost Breakdown</t>
+  </si>
+  <si>
+    <t>Recipient</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Labor</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Permits</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Taxes on labor and on non-fuel goods are handled at the Cross-Sector Totals sheet</t>
+  </si>
+  <si>
+    <t>and should not be taken out here.  Therefore, we reallocate the taxes share</t>
+  </si>
+  <si>
+    <t>proportionately to the other recipients.</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Assigned ISIC Code</t>
+  </si>
+  <si>
+    <t>ISIC Code Meaning</t>
+  </si>
+  <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Other business sector services</t>
+  </si>
+  <si>
+    <t>Validation checks</t>
+  </si>
+  <si>
+    <t>Child-factor groups sum to 1 (per file/context/parent; rate-file reroutes excluded)</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 01T03</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 07T08</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 30</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 49T53</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 69T82</t>
+  </si>
+  <si>
+    <t>EVCRSbRIC.csv | Share of Costs by ISIC Code | ISIC 90T96</t>
   </si>
   <si>
     <t>Unit: %</t>
   </si>
   <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
+    <t>ISIC 05</t>
+  </si>
+  <si>
+    <t>ISIC 06</t>
   </si>
   <si>
     <t>ISIC 09</t>
@@ -82,39 +285,54 @@
     <t>ISIC 19</t>
   </si>
   <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
     <t>ISIC 22</t>
   </si>
   <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
     <t>ISIC 25</t>
   </si>
   <si>
     <t>ISIC 26</t>
   </si>
   <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
     <t>ISIC 28</t>
   </si>
   <si>
     <t>ISIC 29</t>
   </si>
   <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
     <t>ISIC 31T33</t>
   </si>
   <si>
-    <t>ISIC 41T43</t>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
   </si>
   <si>
     <t>ISIC 45T47</t>
   </si>
   <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
     <t>ISIC 55T56</t>
   </si>
   <si>
@@ -133,9 +351,6 @@
     <t>ISIC 68</t>
   </si>
   <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
     <t>ISIC 84</t>
   </si>
   <si>
@@ -145,100 +360,7 @@
     <t>ISIC 86T88</t>
   </si>
   <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
     <t>ISIC 97T98</t>
-  </si>
-  <si>
-    <t>Share of Costs by ISIC Code</t>
-  </si>
-  <si>
-    <t>DOE Cost Breakdown</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Recipient</t>
-  </si>
-  <si>
-    <t>Labor</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>Permits</t>
-  </si>
-  <si>
-    <t>Taxes</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Taxes on labor and on non-fuel goods are handled at the Cross-Sector Totals sheet</t>
-  </si>
-  <si>
-    <t>and should not be taken out here.  Therefore, we reallocate the taxes share</t>
-  </si>
-  <si>
-    <t>proportionately to the other recipients.</t>
-  </si>
-  <si>
-    <t>Share</t>
-  </si>
-  <si>
-    <t>Assigned ISIC Code</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>ISIC Code Meaning</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Other business sector services</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
   </si>
 </sst>
 </file>
@@ -248,7 +370,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +393,15 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -298,21 +429,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -627,8 +757,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D0DBC6-BBF6-4FFA-8935-A589DD9D6AFF}">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="68.5703125" customWidth="1"/>
@@ -644,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -654,33 +784,469 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{8781B4B3-37D5-4572-8D6F-14CD46093886}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BEAC16-ACE6-4F2E-B342-922D366B3EB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>0.94299868264323294</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>0.94299868264323294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>4.1765731369656618E-2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4">
+        <v>4.1765731369656618E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>1.523558598711041E-2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>1.523558598711041E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>0.43273688361237522</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>0.43273688361237522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>0.56726311638762483</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>0.56726311638762483</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>0.1171368722490322</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>0.1171368722490322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>0.88286312775096776</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>0.88286312775096776</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>0.47816430118296149</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10">
+        <v>0.47816430118296149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>4.2586393966149647E-2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11">
+        <v>4.2586393966149647E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>0.1808024634415262</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>0.1808024634415262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>0.2139060571318126</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13">
+        <v>0.2139060571318126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14">
+        <v>8.4540784277550088E-2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14">
+        <v>8.4540784277550088E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15">
+        <v>0.72982194479141249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16">
+        <v>0.27017805520858751</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17">
+        <v>0.42162495143522749</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17">
+        <v>0.42162495143522749</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18">
+        <v>0.57837504856477251</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18">
+        <v>0.57837504856477251</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -692,155 +1258,155 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="5">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>0.6</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>AVERAGE(B3:C3)</f>
         <v>0.57499999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="5">
+        <v>51</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.3</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>0.35</v>
       </c>
-      <c r="D4" s="6">
-        <f t="shared" ref="D4:D6" si="0">AVERAGE(B4:C4)</f>
+      <c r="D4" s="5">
+        <f>AVERAGE(B4:C4)</f>
         <v>0.32499999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="5">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.05</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>0.05</v>
       </c>
-      <c r="D5" s="5">
-        <f t="shared" si="0"/>
+      <c r="D5" s="4">
+        <f>AVERAGE(B5:C5)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="5">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.05</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>0.05</v>
       </c>
-      <c r="D6" s="5">
-        <f t="shared" si="0"/>
+      <c r="D6" s="4">
+        <f>AVERAGE(B6:C6)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>54</v>
+      <c r="A12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="6">
+        <v>50</v>
+      </c>
+      <c r="B13" s="5">
         <f>D3+D$6*D3/SUM(D$3:D$5)</f>
         <v>0.60526315789473684</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="6">
-        <f t="shared" ref="B14:B15" si="1">D4+D$6*D4/SUM(D$3:D$5)</f>
+        <v>51</v>
+      </c>
+      <c r="B14" s="5">
+        <f>D4+D$6*D4/SUM(D$3:D$5)</f>
         <v>0.34210526315789469</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="6">
-        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B15" s="5">
+        <f>D5+D$6*D5/SUM(D$3:D$5)</f>
         <v>5.2631578947368425E-2</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -848,160 +1414,294 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098445D0-3D89-4FAB-95C7-941A2E10FAA3}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <f>('Factors applied'!$E$3+'Factors applied'!$E$4+'Factors applied'!$E$5)</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="str">
+        <f t="shared" ref="C4:C9" si="0">IF(ABS(B4-1)&lt;0.000000001,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5">
+        <f>('Factors applied'!$E$6+'Factors applied'!$E$7)</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6">
+        <f>('Factors applied'!$E$8+'Factors applied'!$E$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7">
+        <f>('Factors applied'!$E$10+'Factors applied'!$E$11+'Factors applied'!$E$12+'Factors applied'!$E$13+'Factors applied'!$E$14)</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8">
+        <f>('Factors applied'!$E$15+'Factors applied'!$E$16)</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9">
+        <f>('Factors applied'!$E$17+'Factors applied'!$E$18)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
+    <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="43" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="4" t="s">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="4" t="s">
+      <c r="AH1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AV1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AW1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="BA1" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
       <c r="B2">
+        <f>0*'Factors applied'!$E$3</f>
         <v>0</v>
       </c>
       <c r="C2">
+        <f>0*'Factors applied'!$E$4</f>
         <v>0</v>
       </c>
       <c r="D2">
+        <f>0*'Factors applied'!$E$5</f>
         <v>0</v>
       </c>
       <c r="E2">
@@ -1011,9 +1711,11 @@
         <v>0</v>
       </c>
       <c r="G2">
+        <f>0*'Factors applied'!$E$6</f>
         <v>0</v>
       </c>
       <c r="H2">
+        <f>0*'Factors applied'!$E$7</f>
         <v>0</v>
       </c>
       <c r="I2">
@@ -1053,18 +1755,18 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <f>'DOE Data and Calcs'!B14</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>('DOE Data and Calcs'!B14)</f>
         <v>0.34210526315789469</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
       <c r="Y2">
         <v>0</v>
       </c>
@@ -1072,56 +1774,96 @@
         <v>0</v>
       </c>
       <c r="AA2">
+        <f>0*'Factors applied'!$E$8</f>
         <v>0</v>
       </c>
       <c r="AB2">
+        <f>0*'Factors applied'!$E$9</f>
         <v>0</v>
       </c>
       <c r="AC2">
-        <f>'DOE Data and Calcs'!B13</f>
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <f>('DOE Data and Calcs'!B13)</f>
         <v>0.60526315789473684</v>
       </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AI2">
+        <f>0*'Factors applied'!$E$10</f>
         <v>0</v>
       </c>
       <c r="AJ2">
+        <f>0*'Factors applied'!$E$11</f>
         <v>0</v>
       </c>
       <c r="AK2">
+        <f>0*'Factors applied'!$E$12</f>
         <v>0</v>
       </c>
       <c r="AL2">
-        <f>'DOE Data and Calcs'!B15</f>
+        <f>0*'Factors applied'!$E$13</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f>0*'Factors applied'!$E$14</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f>('DOE Data and Calcs'!B15)*'Factors applied'!$E$15</f>
         <v>5.2631578947368425E-2</v>
       </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
+      <c r="AU2">
+        <f>('DOE Data and Calcs'!B15)*'Factors applied'!$E$16</f>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f>0*'Factors applied'!$E$17</f>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f>0*'Factors applied'!$E$18</f>
+        <v>0</v>
+      </c>
+      <c r="BA2">
         <v>0</v>
       </c>
     </row>
